--- a/artfynd/A 39620-2023 artfynd.xlsx
+++ b/artfynd/A 39620-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39620-2023 artfynd.xlsx
+++ b/artfynd/A 39620-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114398701</v>
+        <v>114398656</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,21 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trosta Gård, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670929</v>
+        <v>670832</v>
       </c>
       <c r="R2" t="n">
-        <v>6615589</v>
+        <v>6615648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hökslag av fasan. Fasanfjädrar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114398584</v>
+        <v>114398407</v>
       </c>
       <c r="B3" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,7 +816,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670888</v>
+        <v>670977</v>
       </c>
       <c r="R3" t="n">
-        <v>6615543</v>
+        <v>6615484</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114398527</v>
+        <v>114398758</v>
       </c>
       <c r="B4" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +902,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102118</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>670944</v>
+        <v>670986</v>
       </c>
       <c r="R4" t="n">
-        <v>6615516</v>
+        <v>6615483</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,15 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114398460</v>
+        <v>114398404</v>
       </c>
       <c r="B5" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,24 +1008,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1057,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670872</v>
+        <v>670902</v>
       </c>
       <c r="R5" t="n">
-        <v>6615543</v>
+        <v>6615558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,17 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Verkar vara en koloni, många här</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,55 +1107,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114398657</v>
+        <v>114398519</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103042</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trosta Gård, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670793</v>
+        <v>670853</v>
       </c>
       <c r="R6" t="n">
-        <v>6615688</v>
+        <v>6615538</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,12 +1172,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hål i myrstack efter gröngöling</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,15 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114398705</v>
+        <v>114398688</v>
       </c>
       <c r="B7" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>670847</v>
+        <v>670989</v>
       </c>
       <c r="R7" t="n">
-        <v>6615695</v>
+        <v>6615508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,15 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114398656</v>
+        <v>114398588</v>
       </c>
       <c r="B8" t="n">
-        <v>57156</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,34 +1330,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>102987</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trosta Gård, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670832</v>
+        <v>670858</v>
       </c>
       <c r="R8" t="n">
-        <v>6615648</v>
+        <v>6615529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,17 +1393,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hökslag av fasan. Fasanfjädrar.</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,32 +1429,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114398585</v>
+        <v>114398526</v>
       </c>
       <c r="B9" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1497,7 +1460,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1506,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670874</v>
+        <v>670934</v>
       </c>
       <c r="R9" t="n">
-        <v>6615598</v>
+        <v>6615503</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,12 +1499,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,37 +1535,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114398536</v>
+        <v>114398528</v>
       </c>
       <c r="B10" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1621,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670930</v>
+        <v>670998</v>
       </c>
       <c r="R10" t="n">
-        <v>6615573</v>
+        <v>6615504</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,15 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114398651</v>
+        <v>114398535</v>
       </c>
       <c r="B11" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1673,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1732,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670908</v>
+        <v>670941</v>
       </c>
       <c r="R11" t="n">
-        <v>6615545</v>
+        <v>6615572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1762,12 +1719,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,15 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114398535</v>
+        <v>114398651</v>
       </c>
       <c r="B12" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,11 +1783,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1847,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>670941</v>
+        <v>670908</v>
       </c>
       <c r="R12" t="n">
-        <v>6615572</v>
+        <v>6615545</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,12 +1825,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,37 +1861,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114398404</v>
+        <v>114398536</v>
       </c>
       <c r="B13" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1962,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>670902</v>
+        <v>670930</v>
       </c>
       <c r="R13" t="n">
-        <v>6615558</v>
+        <v>6615573</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,12 +1935,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,43 +1971,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114398341</v>
+        <v>114398550</v>
       </c>
       <c r="B14" t="n">
-        <v>57885</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2073,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>670948</v>
+        <v>670850</v>
       </c>
       <c r="R14" t="n">
-        <v>6615543</v>
+        <v>6615709</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,12 +2041,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ungar flyger runt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,32 +2082,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114398416</v>
+        <v>114398341</v>
       </c>
       <c r="B15" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2172,11 +2110,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -2188,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>670857</v>
+        <v>670948</v>
       </c>
       <c r="R15" t="n">
-        <v>6615554</v>
+        <v>6615543</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,32 +2188,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114398652</v>
+        <v>114398657</v>
       </c>
       <c r="B16" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2299,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>670881</v>
+        <v>670793</v>
       </c>
       <c r="R16" t="n">
-        <v>6615587</v>
+        <v>6615688</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,32 +2294,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114398683</v>
+        <v>114398701</v>
       </c>
       <c r="B17" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2410,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>670865</v>
+        <v>670929</v>
       </c>
       <c r="R17" t="n">
-        <v>6615548</v>
+        <v>6615589</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,6 +2393,1409 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114398416</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>670857</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6615554</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114398460</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>670872</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6615543</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Verkar vara en koloni, många här</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114398527</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>670944</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6615516</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114398532</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>670960</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6615562</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114398584</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>670888</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6615543</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114398585</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>670874</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6615598</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114398603</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>670910</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6615654</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114398652</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>670881</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6615587</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>114398660</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>670762</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6615664</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>114398683</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>670865</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6615548</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>114398705</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>670847</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6615695</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>114398417</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>670935</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6615635</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>114398699</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>670962</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6615559</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
         <is>
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>

--- a/artfynd/A 39620-2023 artfynd.xlsx
+++ b/artfynd/A 39620-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398656</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398407</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398758</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398404</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398519</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398688</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398588</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398526</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398528</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398535</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398651</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398536</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2079,6 +2144,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398550</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,6 +2255,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398341</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2291,6 +2366,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398657</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2397,6 +2477,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398701</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2507,6 +2592,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398416</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2618,6 +2708,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398460</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2724,6 +2819,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398527</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2834,6 +2934,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398532</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2944,6 +3049,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398584</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3050,6 +3160,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398585</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3160,6 +3275,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398603</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3266,6 +3386,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398652</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3372,6 +3497,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398660</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3478,6 +3608,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398683</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3584,6 +3719,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398705</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3694,6 +3834,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398417</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3800,8 +3945,44 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398699</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>